--- a/forms/trg/Formulir_TRG_float-struc.xlsx
+++ b/forms/trg/Formulir_TRG_float-struc.xlsx
@@ -955,7 +955,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Member</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
